--- a/pin assignment.xlsx
+++ b/pin assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco\Documents\RAPID-Git\pcbs\rapid_io_module\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3F9B85-9BFE-4810-AFE5-607478B6E840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7D5A3B-4321-4FD1-A118-30232C6F818B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{1C9C7380-D03C-4042-9D8A-EFFEB03C784E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C9C7380-D03C-4042-9D8A-EFFEB03C784E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -1285,7 +1285,7 @@
         <v>80</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>155</v>
@@ -1305,7 +1305,7 @@
         <v>80</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>156</v>
@@ -1782,7 +1782,7 @@
         <v>80</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1805,7 +1805,7 @@
         <v>80</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -2139,7 +2139,7 @@
         <v>83</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>12</v>
@@ -2162,7 +2162,7 @@
         <v>83</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>13</v>

--- a/pin assignment.xlsx
+++ b/pin assignment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco\Documents\RAPID-Git\pcbs\rapid_io_module\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7D5A3B-4321-4FD1-A118-30232C6F818B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8C9C4C-C353-4801-9016-502385C47D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C9C7380-D03C-4042-9D8A-EFFEB03C784E}"/>
   </bookViews>
@@ -605,10 +605,10 @@
     <t>PB03</t>
   </si>
   <si>
-    <t>IO-8 (ADC)</t>
-  </si>
-  <si>
     <t>IO-2</t>
+  </si>
+  <si>
+    <t>I_sense_3 (main voltage current)</t>
   </si>
 </sst>
 </file>
@@ -1635,292 +1635,292 @@
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>83</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
+        <v>56</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
         <v>57</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F25" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G25" s="4" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>58</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>83</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>83</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>83</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
+        <v>62</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>30</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D30" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>33</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
+        <v>33</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
         <v>34</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" s="5" t="s">
+      <c r="C33" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
-        <v>35</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
+        <v>35</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
         <v>36</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D34" s="8" t="s">
+      <c r="C35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
-        <v>55</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>8</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>80</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>171</v>
@@ -2248,7 +2248,7 @@
         <v>80</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>17</v>
